--- a/data/trans_orig/ProbViv_estruc-Clase-trans_orig.xlsx
+++ b/data/trans_orig/ProbViv_estruc-Clase-trans_orig.xlsx
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5910</t>
+          <t>5988</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15306</t>
+          <t>15916</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4088</t>
+          <t>4145</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16254</t>
+          <t>15683</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12189</t>
+          <t>11871</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>28343</t>
+          <t>26686</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,1%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>89156</t>
+          <t>88546</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>98552</t>
+          <t>98474</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,35%</t>
+          <t>84,76%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>119711</t>
+          <t>120282</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>131877</t>
+          <t>131820</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,05%</t>
+          <t>88,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>212083</t>
+          <t>213740</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>228237</t>
+          <t>228555</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,21%</t>
+          <t>88,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>95,06%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1672</t>
+          <t>1622</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9216</t>
+          <t>9372</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3528</t>
+          <t>3707</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12634</t>
+          <t>12422</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7328</t>
+          <t>6880</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>18580</t>
+          <t>18818</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,89%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>85465</t>
+          <t>85309</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>93009</t>
+          <t>93059</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>90,1%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>82939</t>
+          <t>83151</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>92045</t>
+          <t>91866</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,78%</t>
+          <t>87,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>171674</t>
+          <t>171436</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>182926</t>
+          <t>183374</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,23%</t>
+          <t>90,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,38%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1504</t>
+          <t>1542</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7963</t>
+          <t>8115</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2677</t>
+          <t>2621</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13688</t>
+          <t>12779</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>5232</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17209</t>
+          <t>17910</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>15,48%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>43898</t>
+          <t>43746</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>50357</t>
+          <t>50319</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,65%</t>
+          <t>84,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>50165</t>
+          <t>51074</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>61176</t>
+          <t>61232</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>78,56%</t>
+          <t>79,99%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>98505</t>
+          <t>97804</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>110357</t>
+          <t>110482</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,13%</t>
+          <t>84,52%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,48%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10873</t>
+          <t>10438</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>28102</t>
+          <t>27709</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10199</t>
+          <t>10284</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>23104</t>
+          <t>23131</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>23992</t>
+          <t>23524</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>44674</t>
+          <t>44358</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,17%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>189724</t>
+          <t>190117</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>206953</t>
+          <t>207388</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,1%</t>
+          <t>87,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>195168</t>
+          <t>195141</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>208073</t>
+          <t>207988</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,42%</t>
+          <t>89,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>391423</t>
+          <t>391739</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>412105</t>
+          <t>412573</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,76%</t>
+          <t>89,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,61%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11746</t>
+          <t>12082</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>29201</t>
+          <t>29772</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>15992</t>
+          <t>16465</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>33384</t>
+          <t>33317</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>32404</t>
+          <t>31589</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>56370</t>
+          <t>55878</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>19,81%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>90227</t>
+          <t>89656</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>107682</t>
+          <t>107346</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>75,55%</t>
+          <t>75,07%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>89,88%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>129233</t>
+          <t>129300</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>146625</t>
+          <t>146152</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>79,47%</t>
+          <t>79,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,17%</t>
+          <t>89,87%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>225675</t>
+          <t>226167</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>249641</t>
+          <t>250456</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>80,01%</t>
+          <t>80,19%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,51%</t>
+          <t>88,8%</t>
         </is>
       </c>
     </row>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4862</t>
+          <t>4800</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14552</t>
+          <t>14931</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6596</t>
+          <t>6801</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>17675</t>
+          <t>17274</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>13947</t>
+          <t>13258</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>28487</t>
+          <t>28949</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>20,55%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>54343</t>
+          <t>53964</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>64033</t>
+          <t>64095</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>78,88%</t>
+          <t>78,33%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>93,03%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>54328</t>
+          <t>54729</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>65407</t>
+          <t>65202</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>75,45%</t>
+          <t>76,01%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,84%</t>
+          <t>90,55%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>112411</t>
+          <t>111949</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>126951</t>
+          <t>127640</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>79,78%</t>
+          <t>79,45%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,1%</t>
+          <t>90,59%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>49889</t>
+          <t>50049</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>79290</t>
+          <t>79068</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>58683</t>
+          <t>58941</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>88218</t>
+          <t>87344</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>116017</t>
+          <t>115365</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>158647</t>
+          <t>157366</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,2%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>577863</t>
+          <t>578085</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>607264</t>
+          <t>607104</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>87,93%</t>
+          <t>87,97%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>660064</t>
+          <t>660938</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>689599</t>
+          <t>689341</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>88,21%</t>
+          <t>88,33%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>92,12%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1246788</t>
+          <t>1248069</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1289418</t>
+          <t>1290070</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>88,71%</t>
+          <t>88,8%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>91,79%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/ProbViv_estruc-Clase-trans_orig.xlsx
+++ b/data/trans_orig/ProbViv_estruc-Clase-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>7536</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3806</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>13410</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>6,2%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>3,13%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>11,03%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>9848</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>5988</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>15916</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>9,43%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>5,73%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>15,24%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>8787</t>
+          <t>9824</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4145</t>
+          <t>5643</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15683</t>
+          <t>15315</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,22 +795,22 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>18635</t>
+          <t>17359</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11871</t>
+          <t>11085</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>26686</t>
+          <t>24916</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>114081</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>108207</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>117811</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>93,8%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>88,97%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>96,87%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>141</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>94614</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>88546</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>98474</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>90,57%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>84,76%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>94,27%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>127178</t>
+          <t>93103</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>120282</t>
+          <t>87612</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>131820</t>
+          <t>97284</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>90,46%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,47%</t>
+          <t>85,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,22 +908,22 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>221791</t>
+          <t>207186</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>213740</t>
+          <t>199629</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>228555</t>
+          <t>213460</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>121617</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>121617</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>121617</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>157</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>104462</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>104462</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>104462</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>135965</t>
+          <t>102927</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>135965</t>
+          <t>102927</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>135965</t>
+          <t>102927</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>240426</t>
+          <t>224545</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>240426</t>
+          <t>224545</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>240426</t>
+          <t>224545</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>6606</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>3446</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>12171</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>7,23%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>3,77%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>13,32%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>4614</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1622</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>9372</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>4,87%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1,71%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>9,9%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7126</t>
+          <t>4602</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3707</t>
+          <t>1627</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12422</t>
+          <t>9436</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>11741</t>
+          <t>11208</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6880</t>
+          <t>6713</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>18818</t>
+          <t>17735</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,44%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>84792</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>79227</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>87952</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>92,77%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>86,68%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>96,23%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>135</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>90067</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>85309</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>93059</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>95,13%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>90,1%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>98,29%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>88447</t>
+          <t>91944</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>83151</t>
+          <t>87110</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>91866</t>
+          <t>94919</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,0%</t>
+          <t>90,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>178513</t>
+          <t>176736</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>171436</t>
+          <t>170209</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>183374</t>
+          <t>181231</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>90,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,43%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>91398</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>91398</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>91398</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>141</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>94681</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>94681</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>94681</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>95573</t>
+          <t>96546</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>95573</t>
+          <t>96546</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>95573</t>
+          <t>96546</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>190254</t>
+          <t>187944</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>190254</t>
+          <t>187944</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>190254</t>
+          <t>187944</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>3781</t>
+          <t>6402</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1542</t>
+          <t>2766</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8115</t>
+          <t>13456</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>23,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>6367</t>
+          <t>4037</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2621</t>
+          <t>1579</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12779</t>
+          <t>9115</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>10148</t>
+          <t>10440</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5232</t>
+          <t>5030</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17910</t>
+          <t>17602</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,94%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>50539</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>43485</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>54175</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>88,76%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>76,37%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>95,14%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>48080</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>43746</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>50319</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>92,71%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>84,35%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>97,03%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>57486</t>
+          <t>49445</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>51074</t>
+          <t>44367</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>61232</t>
+          <t>51903</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>90,03%</t>
+          <t>92,45%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>79,99%</t>
+          <t>82,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>105566</t>
+          <t>99983</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>97804</t>
+          <t>92821</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>110482</t>
+          <t>105393</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>91,23%</t>
+          <t>90,55%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,52%</t>
+          <t>84,06%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,45%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>56941</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>56941</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>56941</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>51861</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>51861</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>51861</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>63853</t>
+          <t>53482</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>63853</t>
+          <t>53482</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>63853</t>
+          <t>53482</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>115714</t>
+          <t>110423</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>115714</t>
+          <t>110423</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>115714</t>
+          <t>110423</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>14957</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>9325</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>21942</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>7,41%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>4,62%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>10,87%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>17766</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>10438</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>27709</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>8,16%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>4,79%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>12,72%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>15764</t>
+          <t>15629</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10284</t>
+          <t>10523</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>23131</t>
+          <t>23586</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>33530</t>
+          <t>30586</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>23524</t>
+          <t>22503</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>44358</t>
+          <t>39686</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,43%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>261</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>186987</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>180002</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>192619</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>92,59%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>89,13%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>95,38%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>251</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>200060</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>190117</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>207388</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>91,84%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>87,28%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>95,21%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>261</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>202508</t>
+          <t>162954</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>195141</t>
+          <t>154997</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>207988</t>
+          <t>168060</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>91,25%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,4%</t>
+          <t>86,79%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>402567</t>
+          <t>349942</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>391739</t>
+          <t>340842</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>412573</t>
+          <t>358025</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>91,96%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,83%</t>
+          <t>89,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,09%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>285</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>201944</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>201944</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>201944</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>277</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>217826</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>217826</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>217826</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>285</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>218272</t>
+          <t>178583</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>218272</t>
+          <t>178583</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>218272</t>
+          <t>178583</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>436097</t>
+          <t>380528</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>436097</t>
+          <t>380528</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>436097</t>
+          <t>380528</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>22093</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>15202</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>31465</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>14,9%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>10,25%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>21,23%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>18318</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>12082</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>29772</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>15,34%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>10,12%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>24,93%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>23652</t>
+          <t>16046</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>16465</t>
+          <t>10788</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>33317</t>
+          <t>23022</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>41970</t>
+          <t>38139</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>31589</t>
+          <t>29622</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>55878</t>
+          <t>50081</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>18,76%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>126150</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>116778</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>133041</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>85,1%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>78,77%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>89,75%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>155</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>101110</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>89656</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>107346</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>84,66%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>75,07%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>89,88%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>138965</t>
+          <t>102685</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>129300</t>
+          <t>95709</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>146152</t>
+          <t>107943</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>85,46%</t>
+          <t>86,49%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>79,51%</t>
+          <t>80,61%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,87%</t>
+          <t>90,91%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>240075</t>
+          <t>228835</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>226167</t>
+          <t>216893</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>250456</t>
+          <t>237352</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>85,12%</t>
+          <t>85,71%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>80,19%</t>
+          <t>81,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>88,9%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>148243</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>148243</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>148243</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>180</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>119428</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>119428</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>119428</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>162617</t>
+          <t>118731</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>162617</t>
+          <t>118731</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>162617</t>
+          <t>118731</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>282045</t>
+          <t>266974</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>282045</t>
+          <t>266974</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>282045</t>
+          <t>266974</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2435,72 +2435,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>10277</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>5955</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>16072</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>15,05%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>8,72%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>23,54%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>8884</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>4800</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>14931</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>12,9%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>6,97%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>21,67%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>11252</t>
+          <t>9519</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6801</t>
+          <t>5100</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>17274</t>
+          <t>16982</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>20136</t>
+          <t>19796</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>13258</t>
+          <t>14075</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>28949</t>
+          <t>28567</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,6%</t>
         </is>
       </c>
     </row>
@@ -2548,72 +2548,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>58010</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>52215</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>62332</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>84,95%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>76,46%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>91,28%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>86</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>60011</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>53964</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>64095</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>87,1%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>78,33%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>93,03%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>60751</t>
+          <t>60837</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>54729</t>
+          <t>53374</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>65202</t>
+          <t>65256</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>84,37%</t>
+          <t>86,47%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>76,01%</t>
+          <t>75,86%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>92,75%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>120762</t>
+          <t>118848</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>111949</t>
+          <t>110077</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>127640</t>
+          <t>124569</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>85,71%</t>
+          <t>85,72%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>79,45%</t>
+          <t>79,4%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>89,85%</t>
         </is>
       </c>
     </row>
@@ -2661,57 +2661,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>68287</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>68287</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>68287</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>99</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>72003</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>72003</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>72003</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>140898</t>
+          <t>138644</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>140898</t>
+          <t>138644</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>140898</t>
+          <t>138644</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2778,72 +2778,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>67870</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>54704</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>82454</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>9,86%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>7,95%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>11,98%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>92</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>63212</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>50049</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>79068</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>9,62%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>7,62%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>12,03%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>72948</t>
+          <t>59658</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>58941</t>
+          <t>47929</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>87344</t>
+          <t>73762</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>136160</t>
+          <t>127528</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>115365</t>
+          <t>110274</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>157366</t>
+          <t>145423</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,11%</t>
         </is>
       </c>
     </row>
@@ -2891,72 +2891,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>860</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>620560</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>605976</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>633726</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>90,14%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>88,02%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>92,05%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>837</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>593941</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>578085</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>607104</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>90,38%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>87,97%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>92,38%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>860</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>675334</t>
+          <t>560969</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>660938</t>
+          <t>546865</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>689341</t>
+          <t>572698</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>90,39%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>88,33%</t>
+          <t>88,11%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>92,28%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1269275</t>
+          <t>1181529</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1248069</t>
+          <t>1163634</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1290070</t>
+          <t>1198783</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>90,31%</t>
+          <t>90,26%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>88,89%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>91,79%</t>
+          <t>91,58%</t>
         </is>
       </c>
     </row>
@@ -3004,57 +3004,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>958</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>688430</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>688430</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>688430</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>929</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>657153</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>657153</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>657153</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>958</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>748282</t>
+          <t>620627</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>748282</t>
+          <t>620627</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>748282</t>
+          <t>620627</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1405435</t>
+          <t>1309057</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1405435</t>
+          <t>1309057</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1405435</t>
+          <t>1309057</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
